--- a/schoolDocs/StudentImportData/Class8_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class8_ImportReady.xlsx
@@ -703,27 +703,27 @@
   <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="25.851" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="36.42" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="135.538" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="25.851" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="9.283" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="11.711" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="25.851" customWidth="true" style="0"/>
+    <col min="17" max="17" width="36.42" customWidth="true" style="0"/>
+    <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="135.538" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -810,6 +810,8 @@
       <c r="H2" t="s">
         <v>25</v>
       </c>
+      <c r="I2"/>
+      <c r="J2"/>
       <c r="K2">
         <v>16200</v>
       </c>
@@ -848,8 +850,10 @@
       <c r="H3" t="s">
         <v>32</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
       <c r="K3">
-        <v>12200</v>
+        <v>16200</v>
       </c>
       <c r="L3" t="s">
         <v>33</v>
@@ -883,6 +887,8 @@
       <c r="H4" t="s">
         <v>25</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4">
         <v>16200</v>
       </c>
@@ -921,6 +927,8 @@
       <c r="H5" t="s">
         <v>25</v>
       </c>
+      <c r="I5"/>
+      <c r="J5"/>
       <c r="K5">
         <v>16200</v>
       </c>
@@ -959,6 +967,8 @@
       <c r="H6" t="s">
         <v>25</v>
       </c>
+      <c r="I6"/>
+      <c r="J6"/>
       <c r="K6">
         <v>2000</v>
       </c>
@@ -1000,6 +1010,8 @@
       <c r="H7" t="s">
         <v>32</v>
       </c>
+      <c r="I7"/>
+      <c r="J7"/>
       <c r="K7">
         <v>16200</v>
       </c>
@@ -1035,6 +1047,11 @@
       <c r="H8" t="s">
         <v>51</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8">
+        <v>0</v>
+      </c>
       <c r="L8" t="s">
         <v>52</v>
       </c>
@@ -1067,8 +1084,10 @@
       <c r="H9" t="s">
         <v>25</v>
       </c>
+      <c r="I9"/>
+      <c r="J9"/>
       <c r="K9">
-        <v>8000</v>
+        <v>16200</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -1105,6 +1124,11 @@
       <c r="H10" t="s">
         <v>51</v>
       </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10">
+        <v>0</v>
+      </c>
       <c r="L10" t="s">
         <v>61</v>
       </c>
@@ -1137,6 +1161,11 @@
       <c r="H11" t="s">
         <v>51</v>
       </c>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11">
+        <v>0</v>
+      </c>
       <c r="L11" t="s">
         <v>65</v>
       </c>
@@ -1181,6 +1210,7 @@
       <c r="I12">
         <v>25</v>
       </c>
+      <c r="J12"/>
       <c r="K12">
         <v>9150</v>
       </c>
@@ -1225,8 +1255,9 @@
       <c r="I13">
         <v>25</v>
       </c>
+      <c r="J13"/>
       <c r="K13" s="5">
-        <v>5000</v>
+        <v>9150</v>
       </c>
       <c r="L13" t="s">
         <v>73</v>
@@ -1266,6 +1297,11 @@
       <c r="H14" t="s">
         <v>51</v>
       </c>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14">
+        <v>0</v>
+      </c>
       <c r="L14" t="s">
         <v>78</v>
       </c>
@@ -1307,6 +1343,8 @@
       <c r="H15" t="s">
         <v>25</v>
       </c>
+      <c r="I15"/>
+      <c r="J15"/>
       <c r="K15">
         <v>12200</v>
       </c>
@@ -1348,8 +1386,10 @@
       <c r="H16" t="s">
         <v>25</v>
       </c>
+      <c r="I16"/>
+      <c r="J16"/>
       <c r="K16" s="5">
-        <v>10000</v>
+        <v>12200</v>
       </c>
       <c r="L16" t="s">
         <v>85</v>
@@ -1389,6 +1429,8 @@
       <c r="H17" t="s">
         <v>25</v>
       </c>
+      <c r="I17"/>
+      <c r="J17"/>
       <c r="K17">
         <v>12200</v>
       </c>
@@ -1430,8 +1472,12 @@
       <c r="H18" t="s">
         <v>68</v>
       </c>
+      <c r="I18"/>
       <c r="J18">
         <v>3000</v>
+      </c>
+      <c r="K18">
+        <v>3000.0</v>
       </c>
       <c r="L18" t="s">
         <v>94</v>

--- a/schoolDocs/StudentImportData/Class8_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class8_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="91">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Tanmay Tele</t>
@@ -125,9 +151,6 @@
     <t>15km</t>
   </si>
   <si>
-    <t>DGA shows ₹12200 for this COC boy (girls rate). System will charge ₹16200. Please verify.</t>
-  </si>
-  <si>
     <t>Zaid Ansari</t>
   </si>
   <si>
@@ -155,18 +178,12 @@
     <t>Shepherd</t>
   </si>
   <si>
-    <t>Partial — ₹2000 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Elvish John</t>
   </si>
   <si>
     <t>23/01/2018</t>
   </si>
   <si>
-    <t>COC student — full ₹16200 collected</t>
-  </si>
-  <si>
     <t>Dhondiram Suryawanshi</t>
   </si>
   <si>
@@ -182,7 +199,7 @@
     <t>6km</t>
   </si>
   <si>
-    <t>DGA shows ₹0 total with FREE marker. Treated as RTE. Please verify correct category.</t>
+    <t>25MS000050</t>
   </si>
   <si>
     <t>Darshan Lakade</t>
@@ -191,9 +208,6 @@
     <t>14/01/2018</t>
   </si>
   <si>
-    <t>Partial — ₹8000 of ₹16200 collected</t>
-  </si>
-  <si>
     <t>Shreya Gaikwad</t>
   </si>
   <si>
@@ -206,7 +220,7 @@
     <t>Bhandgaon</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000051</t>
   </si>
   <si>
     <t>Manjiri Kamble</t>
@@ -218,6 +232,9 @@
     <t>Works at hospital</t>
   </si>
   <si>
+    <t>25MS000052</t>
+  </si>
+  <si>
     <t>Umera Ansari</t>
   </si>
   <si>
@@ -230,9 +247,6 @@
     <t>Road Shop</t>
   </si>
   <si>
-    <t>DGA total ₹9150 (= 25% off ₹12200) but G col blank — assumed 25% discount. Full paid. Please verify.</t>
-  </si>
-  <si>
     <t>Vaishnavi Gardade</t>
   </si>
   <si>
@@ -245,9 +259,6 @@
     <t>Parlour</t>
   </si>
   <si>
-    <t>DGA total ₹9150 (= 25% off ₹12200) but G col blank — assumed 25% discount. Collected ₹5000 partial. Please verify.</t>
-  </si>
-  <si>
     <t>Arti Suryavanshi</t>
   </si>
   <si>
@@ -260,6 +271,9 @@
     <t>Supporting staff at DGA</t>
   </si>
   <si>
+    <t>25MS000053</t>
+  </si>
+  <si>
     <t>Dhruti Patel</t>
   </si>
   <si>
@@ -278,9 +292,6 @@
     <t>Railway Employee</t>
   </si>
   <si>
-    <t>Partial — ₹10000 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Tanaya Dhaygude</t>
   </si>
   <si>
@@ -303,9 +314,6 @@
   </si>
   <si>
     <t>Works at wages (single parent)</t>
-  </si>
-  <si>
-    <t>Custom fee ₹3000 — single parent household. Collected ₹0. Please verify with school.</t>
   </si>
 </sst>
 </file>
@@ -357,12 +365,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -370,6 +372,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -391,16 +399,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,7 +731,7 @@
     <col min="18" max="18" width="28.136" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="135.538" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -757,10 +765,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -787,7 +795,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -830,6 +838,7 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
@@ -864,16 +873,14 @@
       <c r="N3" t="s">
         <v>35</v>
       </c>
-      <c r="U3" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="U3" s="4"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -893,7 +900,7 @@
         <v>16200</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s">
         <v>27</v>
@@ -902,18 +909,19 @@
         <v>28</v>
       </c>
       <c r="P4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -933,7 +941,7 @@
         <v>16200</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M5" t="s">
         <v>27</v>
@@ -942,18 +950,19 @@
         <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
       </c>
+      <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -973,7 +982,7 @@
         <v>2000</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
         <v>27</v>
@@ -982,21 +991,19 @@
         <v>28</v>
       </c>
       <c r="P6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
       </c>
-      <c r="U6" t="s">
-        <v>46</v>
-      </c>
+      <c r="U6"/>
     </row>
     <row r="7" spans="1:21">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -1016,7 +1023,7 @@
         <v>16200</v>
       </c>
       <c r="L7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M7" t="s">
         <v>34</v>
@@ -1024,16 +1031,14 @@
       <c r="N7" t="s">
         <v>35</v>
       </c>
-      <c r="U7" t="s">
-        <v>49</v>
-      </c>
+      <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>22</v>
@@ -1045,7 +1050,7 @@
         <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1053,16 +1058,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="M8" t="s">
-        <v>53</v>
-      </c>
-      <c r="N8" t="s">
-        <v>54</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1070,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
@@ -1090,7 +1095,7 @@
         <v>16200</v>
       </c>
       <c r="L9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M9" t="s">
         <v>27</v>
@@ -1098,19 +1103,17 @@
       <c r="N9" t="s">
         <v>28</v>
       </c>
-      <c r="U9" t="s">
-        <v>58</v>
-      </c>
+      <c r="U9"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -1122,7 +1125,7 @@
         <v>8698995856</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1130,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="U10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1147,10 +1150,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -1159,7 +1162,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -1167,16 +1170,16 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="R11" t="s">
         <v>30</v>
@@ -1190,10 +1193,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -1205,7 +1208,7 @@
         <v>9730448092</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I12">
         <v>25</v>
@@ -1215,7 +1218,7 @@
         <v>9150</v>
       </c>
       <c r="L12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M12" t="s">
         <v>27</v>
@@ -1224,24 +1227,22 @@
         <v>28</v>
       </c>
       <c r="P12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R12" t="s">
         <v>30</v>
       </c>
-      <c r="U12" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="U12" s="4"/>
     </row>
     <row r="13" spans="1:21">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1250,17 +1251,17 @@
         <v>24</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I13">
         <v>25</v>
       </c>
       <c r="J13"/>
-      <c r="K13" s="5">
+      <c r="K13" s="4">
         <v>9150</v>
       </c>
       <c r="L13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M13" t="s">
         <v>27</v>
@@ -1269,24 +1270,22 @@
         <v>28</v>
       </c>
       <c r="P13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R13" t="s">
-        <v>75</v>
-      </c>
-      <c r="U13" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="U13" s="4"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1295,7 +1294,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -1303,22 +1302,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="R14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U14" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1326,10 +1325,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1349,7 +1348,7 @@
         <v>12200</v>
       </c>
       <c r="L15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="M15" t="s">
         <v>27</v>
@@ -1358,21 +1357,22 @@
         <v>28</v>
       </c>
       <c r="P15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
       </c>
+      <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1388,11 +1388,11 @@
       </c>
       <c r="I16"/>
       <c r="J16"/>
-      <c r="K16" s="5">
+      <c r="K16" s="4">
         <v>12200</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M16" t="s">
         <v>27</v>
@@ -1401,24 +1401,22 @@
         <v>28</v>
       </c>
       <c r="P16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
       </c>
-      <c r="U16" t="s">
-        <v>87</v>
-      </c>
+      <c r="U16"/>
     </row>
     <row r="17" spans="1:21">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
         <v>23</v>
@@ -1435,30 +1433,31 @@
         <v>12200</v>
       </c>
       <c r="L17" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="M17" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="N17" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="R17" t="s">
         <v>30</v>
       </c>
+      <c r="U17"/>
     </row>
     <row r="18" spans="1:21">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
@@ -1470,7 +1469,7 @@
         <v>9860528549</v>
       </c>
       <c r="H18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I18"/>
       <c r="J18">
@@ -1480,14 +1479,12 @@
         <v>3000.0</v>
       </c>
       <c r="L18" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="Q18" t="s">
-        <v>95</v>
-      </c>
-      <c r="U18" s="5" t="s">
-        <v>96</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="U18" s="4"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -1501,6 +1498,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>
--- a/schoolDocs/StudentImportData/Class8_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/Class8_ImportReady.xlsx
@@ -838,6 +838,9 @@
       <c r="R2" t="s">
         <v>30</v>
       </c>
+      <c r="S2">
+        <v>27000010145</v>
+      </c>
       <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
@@ -873,6 +876,9 @@
       <c r="N3" t="s">
         <v>35</v>
       </c>
+      <c r="S3">
+        <v>27000010146</v>
+      </c>
       <c r="U3" s="4"/>
     </row>
     <row r="4" spans="1:21">
@@ -914,6 +920,9 @@
       <c r="R4" t="s">
         <v>30</v>
       </c>
+      <c r="S4">
+        <v>27000010147</v>
+      </c>
       <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
@@ -955,6 +964,9 @@
       <c r="R5" t="s">
         <v>30</v>
       </c>
+      <c r="S5">
+        <v>27000010148</v>
+      </c>
       <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
@@ -996,6 +1008,9 @@
       <c r="R6" t="s">
         <v>30</v>
       </c>
+      <c r="S6">
+        <v>27000010149</v>
+      </c>
       <c r="U6"/>
     </row>
     <row r="7" spans="1:21">
@@ -1031,6 +1046,9 @@
       <c r="N7" t="s">
         <v>35</v>
       </c>
+      <c r="S7">
+        <v>27000010150</v>
+      </c>
       <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
@@ -1066,6 +1084,9 @@
       <c r="N8" t="s">
         <v>51</v>
       </c>
+      <c r="S8">
+        <v>27000010151</v>
+      </c>
       <c r="U8" s="4" t="s">
         <v>52</v>
       </c>
@@ -1103,6 +1124,9 @@
       <c r="N9" t="s">
         <v>28</v>
       </c>
+      <c r="S9">
+        <v>27000010152</v>
+      </c>
       <c r="U9"/>
     </row>
     <row r="10" spans="1:21">
@@ -1141,6 +1165,9 @@
       <c r="N10" t="s">
         <v>51</v>
       </c>
+      <c r="S10">
+        <v>27000010153</v>
+      </c>
       <c r="U10" t="s">
         <v>59</v>
       </c>
@@ -1184,6 +1211,9 @@
       <c r="R11" t="s">
         <v>30</v>
       </c>
+      <c r="S11">
+        <v>27000010154</v>
+      </c>
       <c r="U11" t="s">
         <v>63</v>
       </c>
@@ -1232,6 +1262,9 @@
       <c r="R12" t="s">
         <v>30</v>
       </c>
+      <c r="S12">
+        <v>27000010155</v>
+      </c>
       <c r="U12" s="4"/>
     </row>
     <row r="13" spans="1:21">
@@ -1274,6 +1307,9 @@
       </c>
       <c r="R13" t="s">
         <v>71</v>
+      </c>
+      <c r="S13">
+        <v>27000010156</v>
       </c>
       <c r="U13" s="4"/>
     </row>
@@ -1316,6 +1352,9 @@
       <c r="R14" t="s">
         <v>75</v>
       </c>
+      <c r="S14">
+        <v>27000010157</v>
+      </c>
       <c r="U14" t="s">
         <v>76</v>
       </c>
@@ -1362,6 +1401,9 @@
       <c r="R15" t="s">
         <v>30</v>
       </c>
+      <c r="S15">
+        <v>27000010158</v>
+      </c>
       <c r="U15"/>
     </row>
     <row r="16" spans="1:21">
@@ -1406,6 +1448,9 @@
       <c r="R16" t="s">
         <v>30</v>
       </c>
+      <c r="S16">
+        <v>27000010159</v>
+      </c>
       <c r="U16"/>
     </row>
     <row r="17" spans="1:21">
@@ -1447,6 +1492,9 @@
       <c r="R17" t="s">
         <v>30</v>
       </c>
+      <c r="S17">
+        <v>27000010160</v>
+      </c>
       <c r="U17"/>
     </row>
     <row r="18" spans="1:21">
@@ -1483,6 +1531,9 @@
       </c>
       <c r="Q18" t="s">
         <v>90</v>
+      </c>
+      <c r="S18">
+        <v>27000010161</v>
       </c>
       <c r="U18" s="4"/>
     </row>
